--- a/IT23672314_Assignment 1 - Test cases.xlsx
+++ b/IT23672314_Assignment 1 - Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Minindu\Desktop\IT23672314-ITPM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE4063A-731E-44B8-8711-05F57F7DF5D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBB557E-6C65-4F1A-AA49-7F8F80E8D454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1231,6 +1231,7 @@
   <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="79.7109375" customWidth="1"/>
     <col min="4" max="4" width="72" customWidth="1"/>
